--- a/data/viajes/Pasajeros 06-Jun-2026.xlsx
+++ b/data/viajes/Pasajeros 06-Jun-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Carga Tren/Pasajeros/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{5E32FDB2-86A1-4732-AA4E-F111A60D6D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1F15B62-77E1-41F3-9A6B-43215154A6B0}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{5E32FDB2-86A1-4732-AA4E-F111A60D6D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E5B589F-B3C6-4EB9-BEE4-E897436CC336}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="56">
   <si>
     <t>Viajes por Contrato</t>
   </si>
@@ -2823,19 +2823,19 @@
         <v>54</v>
       </c>
       <c r="B33" s="2">
-        <v>422</v>
+        <v>2016</v>
       </c>
       <c r="C33" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" s="2">
-        <v>5440</v>
+        <v>39839</v>
       </c>
       <c r="E33" s="2">
-        <v>134</v>
+        <v>581</v>
       </c>
       <c r="F33" s="2">
-        <v>1428</v>
+        <v>6448</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>1</v>
@@ -2847,49 +2847,49 @@
         <v>1</v>
       </c>
       <c r="J33" s="2">
-        <v>3294</v>
+        <v>22958</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>433</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>1</v>
+        <v>2434</v>
+      </c>
+      <c r="M33" s="2">
+        <v>2</v>
       </c>
       <c r="N33" s="2">
+        <v>10</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>364</v>
+      </c>
+      <c r="R33" s="2">
+        <v>17</v>
+      </c>
+      <c r="S33" s="2">
+        <v>45</v>
+      </c>
+      <c r="T33" s="2">
         <v>4</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>43</v>
-      </c>
-      <c r="R33" s="2">
-        <v>6</v>
-      </c>
-      <c r="S33" s="2">
-        <v>15</v>
-      </c>
-      <c r="T33" s="2">
-        <v>1</v>
-      </c>
       <c r="U33" s="2">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="V33" s="2">
-        <v>176</v>
+        <v>457</v>
       </c>
       <c r="W33" s="2">
-        <v>492</v>
+        <v>1251</v>
       </c>
       <c r="X33" s="2">
-        <v>124</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -2901,19 +2901,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -3160,6 +3147,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3170,17 +3170,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5BA818-F0FF-496D-B882-BA977B7C1DF2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409317F8-EDFD-4EF4-AAD6-146663BFC2B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3199,6 +3188,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5BA818-F0FF-496D-B882-BA977B7C1DF2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB24654B-EEF5-4E2F-902E-CD6AB81AF804}">
   <ds:schemaRefs>
